--- a/full_report_MiniMax-M2.5_LONG-001.xlsx
+++ b/full_report_MiniMax-M2.5_LONG-001.xlsx
@@ -484,23 +484,23 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>超长输出请求异常：400 Client Error: Bad Request for url: https://ws-cfn2wogecpd5nvb1.cn-beijing.maas.aliyuncs.com/compatible-mode/v1/chat/completions</t>
+          <t>超长输出未达标，实际输出4924tokens仅覆盖目标的16.4%</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>4924</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0</v>
+        <v>43.33</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>690.58</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0</v>
+        <v>23.08</v>
       </c>
     </row>
   </sheetData>
